--- a/branches/migration/2027.0.0-alpha.6-template-v0.13.2/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
+++ b/branches/migration/2027.0.0-alpha.6-template-v0.13.2/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:01:27+00:00</t>
+    <t>2026-09-02T09:13:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-alpha.6-template-v0.13.2/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
+++ b/branches/migration/2027.0.0-alpha.6-template-v0.13.2/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:13:42+00:00</t>
+    <t>2026-09-02T09:46:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-alpha.6-template-v0.13.2/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
+++ b/branches/migration/2027.0.0-alpha.6-template-v0.13.2/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:46:11+00:00</t>
+    <t>2026-09-02T09:54:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-alpha.6-template-v0.13.2/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
+++ b/branches/migration/2027.0.0-alpha.6-template-v0.13.2/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:54:50+00:00</t>
+    <t>2026-09-02T10:49:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-alpha.6-template-v0.13.2/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
+++ b/branches/migration/2027.0.0-alpha.6-template-v0.13.2/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:49:18+00:00</t>
+    <t>2026-09-02T11:53:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-alpha.6-template-v0.13.2/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
+++ b/branches/migration/2027.0.0-alpha.6-template-v0.13.2/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T11:53:33+00:00</t>
+    <t>2026-09-02T12:13:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-alpha.6-template-v0.13.2/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
+++ b/branches/migration/2027.0.0-alpha.6-template-v0.13.2/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T12:13:25+00:00</t>
+    <t>2026-09-02T12:45:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-alpha.6-template-v0.13.2/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
+++ b/branches/migration/2027.0.0-alpha.6-template-v0.13.2/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$117</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4359" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3807" uniqueCount="536">
   <si>
     <t>Property</t>
   </si>
@@ -63,19 +63,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T12:45:31+00:00</t>
+    <t>2026-09-02T21:03:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>NUM-DIZ</t>
+    <t>Medizininformatik Initiative</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>NUM-DIZ (https://www.netzwerk-universitaetsmedizin.de)</t>
+    <t>Medizininformatik Initiative (https://www.medizininformatik-initiative.de)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -295,6 +295,14 @@
     <t>Resource.id</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
     <t>DiagnosticReport.meta</t>
   </si>
   <si>
@@ -309,14 +317,6 @@
   </si>
   <si>
     <t>Resource.meta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
   </si>
   <si>
     <t>DiagnosticReport.meta.id</t>
@@ -1011,7 +1011,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+ref-1:SHALL have a contained resource if a local reference is provided {reference.exists() implies (reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids')) or (reference='#' and %rootResource!=%resource))}</t>
   </si>
   <si>
     <t>DiagnosticReport.basedOn</t>
@@ -1161,94 +1161,24 @@
 </t>
   </si>
   <si>
-    <t>DiagnosticReport.category:lab-category</t>
-  </si>
-  <si>
-    <t>lab-category</t>
+    <t>DiagnosticReport.category:v2-lab</t>
+  </si>
+  <si>
+    <t>v2-lab</t>
   </si>
   <si>
     <t>Labor-Kategorie</t>
   </si>
   <si>
-    <t>Kategorie-Slice für Laborbefunde</t>
+    <t>Die verpflichtende Kategorie des Laborbefunds. Weitere Codings im selben Eintrag und weitere category-Eintraege sind zulaessig.</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://loinc.org"/&gt;
-    &lt;code value="26436-6"/&gt;
-  &lt;/coding&gt;
   &lt;coding&gt;
     &lt;system value="http://terminology.hl7.org/CodeSystem/v2-0074"/&gt;
     &lt;code value="LAB"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:lab-category.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:lab-category.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:lab-category.coding</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.coding</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:lab-category.coding.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.coding.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:lab-category.coding.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.coding.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:lab-category.coding.system</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.coding.system</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:lab-category.coding.version</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.coding.version</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:lab-category.coding.code</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.coding.code</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:lab-category.coding.display</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.coding.display</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:lab-category.coding.userSelected</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.coding.userSelected</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:lab-category.text</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.text</t>
   </si>
   <si>
     <t>DiagnosticReport.category:mibi-category</t>
@@ -1271,42 +1201,6 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>DiagnosticReport.category:mibi-category.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:mibi-category.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:mibi-category.coding</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:mibi-category.coding:v2-microbiology</t>
-  </si>
-  <si>
-    <t>v2-microbiology</t>
-  </si>
-  <si>
-    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="http://terminology.hl7.org/CodeSystem/v2-0074"/&gt;
-  &lt;code value="MB"/&gt;
-&lt;/valueCoding&gt;</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:mibi-category.coding:loinc-microbiology-studies</t>
-  </si>
-  <si>
-    <t>loinc-microbiology-studies</t>
-  </si>
-  <si>
-    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="http://loinc.org"/&gt;
-  &lt;code value="18725-2"/&gt;
-&lt;/valueCoding&gt;</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:mibi-category.text</t>
-  </si>
-  <si>
     <t>DiagnosticReport.category:mibi-sub-category</t>
   </si>
   <si>
@@ -1316,7 +1210,7 @@
     <t>Mikrobiologie-Kategorie LOINC</t>
   </si>
   <si>
-    <t>Kategorie-Slice für die LOINC-Kodierung von mikrobiologischen Befunden. Mehrfachangabe zulaessig, wenn der Befund mehrere Studientypen umfasst, z. B. bakteriologisch und mykologisch. Umfasst der Befund keine benennbaren Studientypen oder soll er nur allgemein eingeordnet werden, entfaellt der Subtyp; die allgemeine Einordnung erfolgt ueber category[mibi-category] mit MB und 18725-2.</t>
+    <t>Kategorie-Slice für die LOINC-Kodierung von mikrobiologischen Befunden. Mehrfachangabe zulaessig, wenn der Befund mehrere Studientypen umfasst, z. B. bakteriologisch und mykologisch. Umfasst der Befund keine benennbaren Studientypen oder soll er nur allgemein eingeordnet werden, entfaellt der Subtyp; die allgemeine Einordnung erfolgt dann allein ueber category[mibi-category] mit MB.</t>
   </si>
   <si>
     <t>https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/ValueSet/mii-vs-mikrobio-befundtyp-loinc</t>
@@ -2138,10 +2032,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ134"/>
+  <dimension ref="A1:AJ117"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="60.296875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="56.33984375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="42.53515625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="24.5234375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="53.34375" customWidth="true" bestFit="true" hidden="true"/>
@@ -2486,18 +2380,18 @@
         <v>84</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>77</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2520,13 +2414,13 @@
         <v>85</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2577,7 +2471,7 @@
         <v>77</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>75</v>
@@ -2586,10 +2480,10 @@
         <v>84</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" hidden="true">
@@ -2788,7 +2682,7 @@
         <v>76</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>113</v>
@@ -2890,10 +2784,10 @@
         <v>84</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" hidden="true">
@@ -2992,10 +2886,10 @@
         <v>84</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9">
@@ -3094,10 +2988,10 @@
         <v>84</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10">
@@ -3196,10 +3090,10 @@
         <v>76</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" hidden="true">
@@ -3298,10 +3192,10 @@
         <v>76</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" hidden="true">
@@ -3400,10 +3294,10 @@
         <v>76</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" hidden="true">
@@ -3502,10 +3396,10 @@
         <v>84</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" hidden="true">
@@ -3604,10 +3498,10 @@
         <v>84</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" hidden="true">
@@ -3706,10 +3600,10 @@
         <v>84</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" hidden="true">
@@ -3910,7 +3804,7 @@
         <v>76</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>113</v>
@@ -4014,7 +3908,7 @@
         <v>76</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>113</v>
@@ -4116,10 +4010,10 @@
         <v>76</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20">
@@ -4222,10 +4116,10 @@
         <v>76</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" hidden="true">
@@ -4424,7 +4318,7 @@
         <v>76</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>113</v>
@@ -4528,10 +4422,10 @@
         <v>84</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24">
@@ -4632,10 +4526,10 @@
         <v>84</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" hidden="true">
@@ -4834,7 +4728,7 @@
         <v>76</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>113</v>
@@ -4936,10 +4830,10 @@
         <v>76</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28">
@@ -5042,10 +4936,10 @@
         <v>76</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" hidden="true">
@@ -5244,7 +5138,7 @@
         <v>76</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>113</v>
@@ -5348,10 +5242,10 @@
         <v>84</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" hidden="true">
@@ -5450,10 +5344,10 @@
         <v>84</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33">
@@ -5554,10 +5448,10 @@
         <v>84</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" hidden="true">
@@ -5658,10 +5552,10 @@
         <v>84</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="35" hidden="true">
@@ -5762,10 +5656,10 @@
         <v>84</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" hidden="true">
@@ -5866,10 +5760,10 @@
         <v>84</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="37">
@@ -5970,10 +5864,10 @@
         <v>84</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="38">
@@ -6072,10 +5966,10 @@
         <v>84</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39" hidden="true">
@@ -6174,7 +6068,7 @@
         <v>84</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>310</v>
@@ -6276,7 +6170,7 @@
         <v>84</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>318</v>
@@ -6380,7 +6274,7 @@
         <v>76</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>318</v>
@@ -6582,7 +6476,7 @@
         <v>76</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>113</v>
@@ -6687,7 +6581,7 @@
         <v>333</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="45" hidden="true">
@@ -6786,10 +6680,10 @@
         <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="46">
@@ -6888,10 +6782,10 @@
         <v>84</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47" hidden="true">
@@ -6990,10 +6884,10 @@
         <v>84</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="48">
@@ -7094,10 +6988,10 @@
         <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49" hidden="true">
@@ -7194,10 +7088,10 @@
         <v>76</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="50">
@@ -7298,49 +7192,53 @@
         <v>76</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
         <v>370</v>
       </c>
       <c r="B51" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="C51" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>77</v>
+        <v>357</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>99</v>
+        <v>218</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>100</v>
+        <v>372</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>373</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>77</v>
@@ -7350,7 +7248,7 @@
         <v>77</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>77</v>
+        <v>374</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>77</v>
@@ -7365,13 +7263,13 @@
         <v>77</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>77</v>
+        <v>362</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>77</v>
+        <v>363</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
@@ -7389,31 +7287,33 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>102</v>
+        <v>356</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>77</v>
+        <v>92</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="C52" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="D52" t="s" s="2">
-        <v>104</v>
+        <v>357</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7423,25 +7323,25 @@
         <v>76</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>105</v>
+        <v>218</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>106</v>
+        <v>377</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>107</v>
+        <v>378</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>108</v>
+        <v>361</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7467,31 +7367,29 @@
         <v>77</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>77</v>
+        <v>379</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>112</v>
+        <v>356</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>75</v>
@@ -7500,29 +7398,29 @@
         <v>76</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>113</v>
+        <v>92</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>77</v>
+        <v>381</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>358</v>
+        <v>84</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>85</v>
@@ -7534,20 +7432,18 @@
         <v>85</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>138</v>
+        <v>218</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>233</v>
+        <v>64</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>234</v>
+        <v>382</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>77</v>
       </c>
@@ -7571,13 +7467,13 @@
         <v>77</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>77</v>
+        <v>384</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>77</v>
+        <v>385</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>77</v>
@@ -7595,27 +7491,27 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>238</v>
+        <v>380</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7712,10 +7608,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7806,18 +7702,18 @@
         <v>76</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>113</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7828,7 +7724,7 @@
         <v>84</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>85</v>
@@ -7840,19 +7736,19 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -7889,39 +7785,37 @@
         <v>77</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="AC56" s="2"/>
       <c r="AD56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7941,20 +7835,18 @@
         <v>77</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
         <v>99</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>255</v>
+        <v>100</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>257</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8003,7 +7895,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>258</v>
+        <v>102</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>75</v>
@@ -8012,54 +7904,52 @@
         <v>84</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>97</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>160</v>
+        <v>105</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>261</v>
+        <v>106</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>262</v>
+        <v>107</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>264</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>77</v>
       </c>
@@ -8095,39 +7985,39 @@
         <v>77</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>266</v>
+        <v>112</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>97</v>
+        <v>113</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8135,7 +8025,7 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>84</v>
@@ -8150,19 +8040,19 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>270</v>
+        <v>248</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8211,7 +8101,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>75</v>
@@ -8220,18 +8110,18 @@
         <v>84</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8254,20 +8144,18 @@
         <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>275</v>
+        <v>99</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>276</v>
+        <v>255</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>77</v>
       </c>
@@ -8315,7 +8203,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>75</v>
@@ -8324,18 +8212,18 @@
         <v>84</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8343,13 +8231,13 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>77</v>
@@ -8358,19 +8246,19 @@
         <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>99</v>
+        <v>160</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>283</v>
+        <v>261</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>286</v>
+        <v>264</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -8419,7 +8307,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>287</v>
+        <v>266</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>75</v>
@@ -8428,28 +8316,26 @@
         <v>84</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="C62" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>357</v>
+        <v>77</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>84</v>
@@ -8464,18 +8350,20 @@
         <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>218</v>
+        <v>99</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>394</v>
+        <v>269</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>395</v>
+        <v>270</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
       </c>
@@ -8484,7 +8372,7 @@
         <v>77</v>
       </c>
       <c r="S62" t="s" s="2">
-        <v>396</v>
+        <v>77</v>
       </c>
       <c r="T62" t="s" s="2">
         <v>77</v>
@@ -8499,13 +8387,13 @@
         <v>77</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>362</v>
+        <v>77</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>363</v>
+        <v>77</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>77</v>
@@ -8523,27 +8411,27 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>356</v>
+        <v>272</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>371</v>
+        <v>395</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8563,19 +8451,23 @@
         <v>77</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>99</v>
+        <v>275</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>100</v>
+        <v>276</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
       </c>
@@ -8623,7 +8515,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>102</v>
+        <v>280</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>75</v>
@@ -8632,52 +8524,56 @@
         <v>84</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>77</v>
+        <v>92</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="C64" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="D64" t="s" s="2">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>105</v>
+        <v>138</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>106</v>
+        <v>233</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>107</v>
+        <v>234</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>77</v>
       </c>
@@ -8686,7 +8582,7 @@
         <v>77</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>77</v>
+        <v>398</v>
       </c>
       <c r="T64" t="s" s="2">
         <v>77</v>
@@ -8713,19 +8609,19 @@
         <v>77</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>112</v>
+        <v>238</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>75</v>
@@ -8734,10 +8630,10 @@
         <v>76</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>113</v>
+        <v>92</v>
       </c>
     </row>
     <row r="65" hidden="true">
@@ -8745,7 +8641,7 @@
         <v>399</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>375</v>
+        <v>399</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8753,10 +8649,10 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>77</v>
@@ -8768,19 +8664,19 @@
         <v>85</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>233</v>
+        <v>283</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>234</v>
+        <v>284</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>235</v>
+        <v>285</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>236</v>
+        <v>286</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -8817,29 +8713,31 @@
         <v>77</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="AC65" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>238</v>
+        <v>287</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="66">
@@ -8847,13 +8745,11 @@
         <v>400</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="C66" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="D66" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -8872,19 +8768,19 @@
         <v>85</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>138</v>
+        <v>402</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>233</v>
+        <v>403</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>234</v>
+        <v>404</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>235</v>
+        <v>405</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>236</v>
+        <v>406</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -8894,7 +8790,7 @@
         <v>77</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>402</v>
+        <v>77</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>77</v>
@@ -8933,31 +8829,29 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>238</v>
+        <v>400</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>97</v>
+        <v>318</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>404</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>77</v>
       </c>
@@ -8969,29 +8863,25 @@
         <v>84</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>233</v>
+        <v>100</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>77</v>
       </c>
@@ -9000,7 +8890,7 @@
         <v>77</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>405</v>
+        <v>77</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>77</v>
@@ -9039,38 +8929,38 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>238</v>
+        <v>102</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>97</v>
+        <v>77</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>391</v>
+        <v>408</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>77</v>
@@ -9079,23 +8969,21 @@
         <v>77</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>283</v>
+        <v>106</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>284</v>
+        <v>107</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>77</v>
       </c>
@@ -9131,52 +9019,50 @@
         <v>77</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>287</v>
+        <v>112</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>97</v>
+        <v>113</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="C69" t="s" s="2">
-        <v>408</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>357</v>
+        <v>77</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>85</v>
@@ -9188,16 +9074,16 @@
         <v>85</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>218</v>
+        <v>99</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>409</v>
+        <v>329</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>410</v>
+        <v>330</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>361</v>
+        <v>331</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9223,11 +9109,13 @@
         <v>77</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="Y69" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z69" t="s" s="2">
-        <v>411</v>
+        <v>77</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>77</v>
@@ -9245,41 +9133,41 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>356</v>
+        <v>332</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>96</v>
+        <v>333</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>413</v>
+        <v>77</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>77</v>
@@ -9288,16 +9176,16 @@
         <v>85</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>218</v>
+        <v>126</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>64</v>
+        <v>335</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>414</v>
+        <v>336</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>415</v>
+        <v>337</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9323,13 +9211,13 @@
         <v>77</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>416</v>
+        <v>338</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>417</v>
+        <v>339</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>77</v>
@@ -9347,27 +9235,27 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>412</v>
+        <v>340</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9381,24 +9269,26 @@
         <v>84</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>99</v>
+        <v>192</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>100</v>
+        <v>342</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -9447,7 +9337,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>102</v>
+        <v>345</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>75</v>
@@ -9456,29 +9346,29 @@
         <v>84</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>77</v>
+        <v>92</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>77</v>
@@ -9487,19 +9377,19 @@
         <v>77</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>106</v>
+        <v>347</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>107</v>
+        <v>348</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>108</v>
+        <v>349</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -9537,50 +9427,50 @@
         <v>77</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>112</v>
+        <v>350</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>113</v>
+        <v>92</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>77</v>
+        <v>414</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>85</v>
@@ -9592,19 +9482,19 @@
         <v>85</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>138</v>
+        <v>415</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>233</v>
+        <v>416</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>234</v>
+        <v>417</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>235</v>
+        <v>418</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>236</v>
+        <v>419</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>77</v>
@@ -9641,37 +9531,39 @@
         <v>77</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="AC73" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>238</v>
+        <v>413</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>97</v>
+        <v>318</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9768,10 +9660,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9862,7 +9754,7 @@
         <v>76</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>113</v>
@@ -9870,10 +9762,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9881,7 +9773,7 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>84</v>
@@ -9896,20 +9788,18 @@
         <v>85</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>247</v>
+        <v>329</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>248</v>
+        <v>330</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>77</v>
       </c>
@@ -9957,7 +9847,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>252</v>
+        <v>332</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>75</v>
@@ -9966,18 +9856,18 @@
         <v>84</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>96</v>
+        <v>333</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10000,16 +9890,16 @@
         <v>85</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>255</v>
+        <v>335</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>256</v>
+        <v>336</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>257</v>
+        <v>337</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10035,13 +9925,13 @@
         <v>77</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>77</v>
+        <v>338</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>77</v>
+        <v>339</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>77</v>
@@ -10059,7 +9949,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>258</v>
+        <v>340</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>75</v>
@@ -10068,18 +9958,18 @@
         <v>84</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10087,7 +9977,7 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>84</v>
@@ -10102,20 +9992,18 @@
         <v>85</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>261</v>
+        <v>342</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>262</v>
+        <v>343</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>264</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>77</v>
       </c>
@@ -10163,7 +10051,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>266</v>
+        <v>345</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>75</v>
@@ -10172,18 +10060,18 @@
         <v>84</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10197,7 +10085,7 @@
         <v>84</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>77</v>
@@ -10209,17 +10097,15 @@
         <v>99</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>269</v>
+        <v>347</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>270</v>
+        <v>348</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>271</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>77</v>
       </c>
@@ -10267,7 +10153,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>272</v>
+        <v>350</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>75</v>
@@ -10276,32 +10162,32 @@
         <v>84</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>77</v>
+        <v>427</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>77</v>
@@ -10310,19 +10196,19 @@
         <v>85</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>275</v>
+        <v>428</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>276</v>
+        <v>429</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>277</v>
+        <v>430</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>278</v>
+        <v>431</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>279</v>
+        <v>432</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>77</v>
@@ -10371,7 +10257,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>280</v>
+        <v>426</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>75</v>
@@ -10380,56 +10266,50 @@
         <v>84</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="C81" t="s" s="2">
-        <v>429</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>233</v>
+        <v>100</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>77</v>
       </c>
@@ -10438,7 +10318,7 @@
         <v>77</v>
       </c>
       <c r="S81" t="s" s="2">
-        <v>430</v>
+        <v>77</v>
       </c>
       <c r="T81" t="s" s="2">
         <v>77</v>
@@ -10477,38 +10357,38 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>238</v>
+        <v>102</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>97</v>
+        <v>77</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>77</v>
@@ -10517,23 +10397,21 @@
         <v>77</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>283</v>
+        <v>106</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>284</v>
+        <v>107</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>77</v>
       </c>
@@ -10569,47 +10447,49 @@
         <v>77</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>287</v>
+        <v>112</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>97</v>
+        <v>113</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="C83" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="C83" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="D83" t="s" s="2">
-        <v>433</v>
+        <v>104</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>84</v>
@@ -10621,23 +10501,21 @@
         <v>77</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>438</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>77</v>
       </c>
@@ -10685,27 +10563,27 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>432</v>
+        <v>112</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>318</v>
+        <v>113</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10728,13 +10606,13 @@
         <v>77</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>99</v>
+        <v>428</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>100</v>
+        <v>441</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>101</v>
+        <v>441</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -10785,7 +10663,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>102</v>
+        <v>442</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>75</v>
@@ -10800,46 +10678,48 @@
         <v>77</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>104</v>
+        <v>444</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>106</v>
+        <v>445</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>107</v>
+        <v>446</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="O85" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>77</v>
       </c>
@@ -10875,50 +10755,50 @@
         <v>77</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>112</v>
+        <v>443</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>113</v>
+        <v>92</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>77</v>
+        <v>450</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>85</v>
@@ -10930,18 +10810,20 @@
         <v>85</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>99</v>
+        <v>451</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>329</v>
+        <v>452</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>330</v>
+        <v>453</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="O86" s="2"/>
+        <v>454</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>77</v>
       </c>
@@ -10989,27 +10871,27 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>332</v>
+        <v>449</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>333</v>
+        <v>91</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>97</v>
+        <v>318</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>442</v>
+        <v>456</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>442</v>
+        <v>456</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11029,20 +10911,18 @@
         <v>77</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>335</v>
+        <v>100</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>337</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>77</v>
@@ -11067,13 +10947,13 @@
         <v>77</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>338</v>
+        <v>77</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>339</v>
+        <v>77</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>77</v>
@@ -11091,7 +10971,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>340</v>
+        <v>102</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>75</v>
@@ -11100,50 +10980,50 @@
         <v>84</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>97</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>192</v>
+        <v>105</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>342</v>
+        <v>106</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>343</v>
+        <v>107</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>344</v>
+        <v>108</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -11181,39 +11061,39 @@
         <v>77</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>345</v>
+        <v>112</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>97</v>
+        <v>113</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11227,7 +11107,7 @@
         <v>84</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>77</v>
@@ -11239,13 +11119,13 @@
         <v>99</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -11295,7 +11175,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>350</v>
+        <v>332</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>75</v>
@@ -11304,22 +11184,22 @@
         <v>84</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>96</v>
+        <v>333</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>446</v>
+        <v>77</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -11329,7 +11209,7 @@
         <v>84</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>77</v>
@@ -11338,20 +11218,18 @@
         <v>85</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>447</v>
+        <v>126</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>448</v>
+        <v>335</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>449</v>
+        <v>336</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>451</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>77</v>
       </c>
@@ -11375,13 +11253,13 @@
         <v>77</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>77</v>
+        <v>338</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>77</v>
+        <v>339</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>77</v>
@@ -11399,7 +11277,7 @@
         <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>445</v>
+        <v>340</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>75</v>
@@ -11408,18 +11286,18 @@
         <v>84</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>318</v>
+        <v>92</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11433,24 +11311,26 @@
         <v>84</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>99</v>
+        <v>192</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>100</v>
+        <v>342</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N91" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>77</v>
@@ -11499,7 +11379,7 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>102</v>
+        <v>345</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>75</v>
@@ -11508,29 +11388,29 @@
         <v>84</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>77</v>
+        <v>92</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>77</v>
@@ -11539,19 +11419,19 @@
         <v>77</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>106</v>
+        <v>347</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>107</v>
+        <v>348</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>108</v>
+        <v>349</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -11589,50 +11469,50 @@
         <v>77</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>112</v>
+        <v>350</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>113</v>
+        <v>92</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>77</v>
+        <v>463</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>85</v>
@@ -11644,18 +11524,20 @@
         <v>85</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>99</v>
+        <v>451</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>329</v>
+        <v>464</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>330</v>
+        <v>465</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="O93" s="2"/>
+        <v>466</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>77</v>
       </c>
@@ -11703,27 +11585,27 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>332</v>
+        <v>462</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>333</v>
+        <v>91</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>97</v>
+        <v>318</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11734,30 +11616,32 @@
         <v>75</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>126</v>
+        <v>468</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>335</v>
+        <v>469</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>336</v>
+        <v>470</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="O94" s="2"/>
+        <v>471</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>472</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>77</v>
       </c>
@@ -11781,13 +11665,13 @@
         <v>77</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>338</v>
+        <v>77</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>339</v>
+        <v>77</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>77</v>
@@ -11805,27 +11689,27 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>340</v>
+        <v>467</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>97</v>
+        <v>318</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>456</v>
+        <v>473</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>456</v>
+        <v>473</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11839,26 +11723,24 @@
         <v>84</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>192</v>
+        <v>99</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>342</v>
+        <v>100</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>344</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>77</v>
@@ -11907,7 +11789,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>345</v>
+        <v>102</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>75</v>
@@ -11916,29 +11798,29 @@
         <v>84</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>97</v>
+        <v>77</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>457</v>
+        <v>474</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>457</v>
+        <v>474</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>77</v>
@@ -11947,19 +11829,19 @@
         <v>77</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>347</v>
+        <v>106</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>348</v>
+        <v>107</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>349</v>
+        <v>108</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -11997,47 +11879,47 @@
         <v>77</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>350</v>
+        <v>112</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>97</v>
+        <v>113</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>458</v>
+        <v>475</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>458</v>
+        <v>475</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>459</v>
+        <v>77</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G97" t="s" s="2">
         <v>84</v>
@@ -12052,20 +11934,18 @@
         <v>85</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>460</v>
+        <v>99</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>461</v>
+        <v>329</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>462</v>
+        <v>330</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>464</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>77</v>
       </c>
@@ -12113,7 +11993,7 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>458</v>
+        <v>332</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>75</v>
@@ -12122,18 +12002,18 @@
         <v>84</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>96</v>
+        <v>333</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12153,18 +12033,20 @@
         <v>77</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>100</v>
+        <v>335</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N98" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>77</v>
@@ -12189,13 +12071,13 @@
         <v>77</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>77</v>
+        <v>338</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>77</v>
+        <v>339</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>77</v>
@@ -12213,7 +12095,7 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>102</v>
+        <v>340</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>75</v>
@@ -12222,50 +12104,50 @@
         <v>84</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>77</v>
+        <v>92</v>
       </c>
     </row>
-    <row r="99" hidden="true">
+    <row r="99">
       <c r="A99" t="s" s="2">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>105</v>
+        <v>192</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>106</v>
+        <v>342</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>107</v>
+        <v>343</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>108</v>
+        <v>344</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -12303,45 +12185,43 @@
         <v>77</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="AC99" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="AD99" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>112</v>
+        <v>345</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>113</v>
+        <v>92</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>467</v>
+        <v>478</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="C100" t="s" s="2">
-        <v>468</v>
-      </c>
+        <v>478</v>
+      </c>
+      <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -12351,25 +12231,25 @@
         <v>84</v>
       </c>
       <c r="H100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J100" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="I100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J100" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="K100" t="s" s="2">
-        <v>469</v>
+        <v>99</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>470</v>
+        <v>347</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>471</v>
+        <v>348</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>108</v>
+        <v>349</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -12419,41 +12299,41 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>112</v>
+        <v>350</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>113</v>
+        <v>92</v>
       </c>
     </row>
-    <row r="101" hidden="true">
+    <row r="101">
       <c r="A101" t="s" s="2">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>77</v>
+        <v>480</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>77</v>
@@ -12462,16 +12342,20 @@
         <v>77</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>460</v>
+        <v>481</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N101" s="2"/>
-      <c r="O101" s="2"/>
+        <v>483</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>485</v>
+      </c>
       <c r="P101" t="s" s="2">
         <v>77</v>
       </c>
@@ -12519,63 +12403,59 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>77</v>
+        <v>318</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>476</v>
+        <v>77</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>477</v>
+        <v>100</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>480</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>77</v>
       </c>
@@ -12623,7 +12503,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>475</v>
+        <v>102</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>75</v>
@@ -12632,22 +12512,22 @@
         <v>84</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>97</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>482</v>
+        <v>104</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -12657,29 +12537,27 @@
         <v>76</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>483</v>
+        <v>105</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>484</v>
+        <v>106</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>485</v>
+        <v>107</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>487</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>77</v>
       </c>
@@ -12715,19 +12593,19 @@
         <v>77</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="AC103" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="AD103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>481</v>
+        <v>112</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>75</v>
@@ -12736,13 +12614,13 @@
         <v>76</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>318</v>
+        <v>113</v>
       </c>
     </row>
-    <row r="104" hidden="true">
+    <row r="104">
       <c r="A104" t="s" s="2">
         <v>488</v>
       </c>
@@ -12761,24 +12639,26 @@
         <v>84</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K104" t="s" s="2">
         <v>99</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>100</v>
+        <v>329</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N104" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>77</v>
@@ -12827,7 +12707,7 @@
         <v>77</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>102</v>
+        <v>332</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>75</v>
@@ -12836,10 +12716,10 @@
         <v>84</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>77</v>
+        <v>333</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>77</v>
+        <v>92</v>
       </c>
     </row>
     <row r="105" hidden="true">
@@ -12851,14 +12731,14 @@
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>77</v>
@@ -12867,19 +12747,19 @@
         <v>77</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>106</v>
+        <v>335</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>107</v>
+        <v>336</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>108</v>
+        <v>337</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -12905,46 +12785,46 @@
         <v>77</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>77</v>
+        <v>338</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>77</v>
+        <v>339</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>112</v>
+        <v>340</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>113</v>
+        <v>92</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
         <v>490</v>
       </c>
@@ -12963,7 +12843,7 @@
         <v>84</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>77</v>
@@ -12972,16 +12852,16 @@
         <v>85</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>99</v>
+        <v>192</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -13031,7 +12911,7 @@
         <v>77</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>75</v>
@@ -13040,10 +12920,10 @@
         <v>84</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>333</v>
+        <v>91</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="107" hidden="true">
@@ -13074,16 +12954,16 @@
         <v>85</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -13109,13 +12989,13 @@
         <v>77</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>338</v>
+        <v>77</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>339</v>
+        <v>77</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>77</v>
@@ -13133,7 +13013,7 @@
         <v>77</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>75</v>
@@ -13142,13 +13022,13 @@
         <v>84</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
         <v>492</v>
       </c>
@@ -13164,28 +13044,28 @@
         <v>75</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>192</v>
+        <v>493</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>342</v>
+        <v>494</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>343</v>
+        <v>495</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>344</v>
+        <v>496</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -13235,38 +13115,38 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>345</v>
+        <v>492</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>97</v>
+        <v>318</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>77</v>
+        <v>498</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>77</v>
@@ -13278,18 +13158,18 @@
         <v>85</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>99</v>
+        <v>499</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>347</v>
+        <v>500</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="O109" s="2"/>
+        <v>501</v>
+      </c>
+      <c r="N109" s="2"/>
+      <c r="O109" t="s" s="2">
+        <v>502</v>
+      </c>
       <c r="P109" t="s" s="2">
         <v>77</v>
       </c>
@@ -13337,63 +13217,59 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>350</v>
+        <v>497</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>495</v>
+        <v>77</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>483</v>
+        <v>99</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>496</v>
+        <v>100</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>487</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N110" s="2"/>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>77</v>
       </c>
@@ -13441,31 +13317,31 @@
         <v>77</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>494</v>
+        <v>102</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>318</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -13475,7 +13351,7 @@
         <v>76</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>77</v>
@@ -13484,20 +13360,18 @@
         <v>77</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>500</v>
+        <v>105</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>501</v>
+        <v>106</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>502</v>
+        <v>107</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>504</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>77</v>
       </c>
@@ -13533,19 +13407,19 @@
         <v>77</v>
       </c>
       <c r="AB111" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="AC111" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="AD111" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE111" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>499</v>
+        <v>112</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>75</v>
@@ -13554,10 +13428,10 @@
         <v>76</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>318</v>
+        <v>113</v>
       </c>
     </row>
     <row r="112" hidden="true">
@@ -13569,35 +13443,39 @@
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>77</v>
+        <v>506</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I112" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>100</v>
+        <v>507</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N112" s="2"/>
-      <c r="O112" s="2"/>
+        <v>508</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="P112" t="s" s="2">
         <v>77</v>
       </c>
@@ -13645,38 +13523,38 @@
         <v>77</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>102</v>
+        <v>509</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>77</v>
@@ -13688,18 +13566,20 @@
         <v>77</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>106</v>
+        <v>511</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>107</v>
+        <v>512</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="O113" s="2"/>
+        <v>513</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>514</v>
+      </c>
       <c r="P113" t="s" s="2">
         <v>77</v>
       </c>
@@ -13735,39 +13615,39 @@
         <v>77</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>112</v>
+        <v>510</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>113</v>
+        <v>92</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13775,13 +13655,13 @@
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G114" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>77</v>
@@ -13790,16 +13670,16 @@
         <v>85</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>99</v>
+        <v>516</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>329</v>
+        <v>517</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>330</v>
+        <v>518</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>331</v>
+        <v>405</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -13849,31 +13729,31 @@
         <v>77</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>332</v>
+        <v>515</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AH114" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>333</v>
+        <v>91</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>97</v>
+        <v>318</v>
       </c>
     </row>
-    <row r="115" hidden="true">
+    <row r="115">
       <c r="A115" t="s" s="2">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>77</v>
+        <v>520</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -13883,27 +13763,29 @@
         <v>84</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>335</v>
+        <v>521</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>336</v>
+        <v>522</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="O115" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="O115" t="s" s="2">
+        <v>523</v>
+      </c>
       <c r="P115" t="s" s="2">
         <v>77</v>
       </c>
@@ -13927,13 +13809,13 @@
         <v>77</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>338</v>
+        <v>77</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>339</v>
+        <v>77</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>77</v>
@@ -13951,7 +13833,7 @@
         <v>77</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>340</v>
+        <v>519</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>75</v>
@@ -13960,18 +13842,18 @@
         <v>84</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>509</v>
+        <v>524</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>509</v>
+        <v>524</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13982,28 +13864,28 @@
         <v>75</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H116" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I116" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>192</v>
+        <v>218</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>342</v>
+        <v>525</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>343</v>
+        <v>526</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>344</v>
+        <v>383</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -14029,13 +13911,13 @@
         <v>77</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>77</v>
+        <v>527</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>77</v>
+        <v>528</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>77</v>
@@ -14053,27 +13935,27 @@
         <v>77</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>345</v>
+        <v>524</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>510</v>
+        <v>529</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>510</v>
+        <v>529</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14084,7 +13966,7 @@
         <v>75</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>77</v>
@@ -14093,21 +13975,23 @@
         <v>77</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>99</v>
+        <v>530</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>347</v>
+        <v>531</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>348</v>
+        <v>532</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="O117" s="2"/>
+        <v>533</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>534</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>77</v>
       </c>
@@ -14155,1763 +14039,23 @@
         <v>77</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>350</v>
+        <v>529</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="C118" s="2"/>
-      <c r="D118" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="E118" s="2"/>
-      <c r="F118" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="G118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H118" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K118" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="L118" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="P118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q118" s="2"/>
-      <c r="R118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AJ118" t="s" s="2">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="119" hidden="true">
-      <c r="A119" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="C119" s="2"/>
-      <c r="D119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E119" s="2"/>
-      <c r="F119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G119" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K119" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="L119" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N119" s="2"/>
-      <c r="O119" s="2"/>
-      <c r="P119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q119" s="2"/>
-      <c r="R119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF119" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AG119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ119" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="120" hidden="true">
-      <c r="A120" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="C120" s="2"/>
-      <c r="D120" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="E120" s="2"/>
-      <c r="F120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K120" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L120" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="O120" s="2"/>
-      <c r="P120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q120" s="2"/>
-      <c r="R120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AG120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI120" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AJ120" t="s" s="2">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="C121" s="2"/>
-      <c r="D121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E121" s="2"/>
-      <c r="F121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H121" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J121" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K121" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="L121" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="O121" s="2"/>
-      <c r="P121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q121" s="2"/>
-      <c r="R121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="AG121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI121" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="AJ121" t="s" s="2">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="122" hidden="true">
-      <c r="A122" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="C122" s="2"/>
-      <c r="D122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E122" s="2"/>
-      <c r="F122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J122" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K122" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="L122" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="O122" s="2"/>
-      <c r="P122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q122" s="2"/>
-      <c r="R122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="123" hidden="true">
-      <c r="A123" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="C123" s="2"/>
-      <c r="D123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E123" s="2"/>
-      <c r="F123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G123" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J123" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K123" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L123" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O123" s="2"/>
-      <c r="P123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q123" s="2"/>
-      <c r="R123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="AG123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH123" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI123" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="124" hidden="true">
-      <c r="A124" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="C124" s="2"/>
-      <c r="D124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E124" s="2"/>
-      <c r="F124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J124" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K124" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="L124" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="O124" s="2"/>
-      <c r="P124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q124" s="2"/>
-      <c r="R124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="AG124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI124" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AJ124" t="s" s="2">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="125" hidden="true">
-      <c r="A125" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="C125" s="2"/>
-      <c r="D125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E125" s="2"/>
-      <c r="F125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G125" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K125" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="L125" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O125" s="2"/>
-      <c r="P125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q125" s="2"/>
-      <c r="R125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="AG125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH125" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI125" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AJ125" t="s" s="2">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="126" hidden="true">
-      <c r="A126" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="C126" s="2"/>
-      <c r="D126" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="E126" s="2"/>
-      <c r="F126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G126" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H126" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I126" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J126" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K126" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="L126" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N126" s="2"/>
-      <c r="O126" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="P126" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q126" s="2"/>
-      <c r="R126" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S126" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T126" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U126" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V126" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W126" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X126" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z126" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="AG126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH126" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI126" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AJ126" t="s" s="2">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="127" hidden="true">
-      <c r="A127" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="C127" s="2"/>
-      <c r="D127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E127" s="2"/>
-      <c r="F127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K127" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="L127" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N127" s="2"/>
-      <c r="O127" s="2"/>
-      <c r="P127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q127" s="2"/>
-      <c r="R127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF127" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AG127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ127" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="128" hidden="true">
-      <c r="A128" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="C128" s="2"/>
-      <c r="D128" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="E128" s="2"/>
-      <c r="F128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G128" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H128" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I128" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J128" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K128" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L128" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="M128" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="O128" s="2"/>
-      <c r="P128" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q128" s="2"/>
-      <c r="R128" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S128" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T128" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U128" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V128" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W128" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X128" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y128" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z128" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA128" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB128" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AC128" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AD128" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE128" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AF128" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AG128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH128" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI128" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AJ128" t="s" s="2">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="129" hidden="true">
-      <c r="A129" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="C129" s="2"/>
-      <c r="D129" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="E129" s="2"/>
-      <c r="F129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G129" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I129" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J129" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K129" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L129" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="P129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q129" s="2"/>
-      <c r="R129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="AG129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH129" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI129" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AJ129" t="s" s="2">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="130" hidden="true">
-      <c r="A130" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="C130" s="2"/>
-      <c r="D130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E130" s="2"/>
-      <c r="F130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G130" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K130" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="L130" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="P130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q130" s="2"/>
-      <c r="R130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF130" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="AG130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH130" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI130" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AJ130" t="s" s="2">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="131" hidden="true">
-      <c r="A131" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B131" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="C131" s="2"/>
-      <c r="D131" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E131" s="2"/>
-      <c r="F131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="G131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H131" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I131" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J131" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K131" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="L131" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O131" s="2"/>
-      <c r="P131" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q131" s="2"/>
-      <c r="R131" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S131" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T131" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U131" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V131" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W131" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X131" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y131" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z131" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA131" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB131" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC131" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD131" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE131" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF131" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="AG131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI131" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AJ131" t="s" s="2">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="B132" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="C132" s="2"/>
-      <c r="D132" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="E132" s="2"/>
-      <c r="F132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G132" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H132" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K132" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="L132" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="P132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q132" s="2"/>
-      <c r="R132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF132" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="AG132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH132" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI132" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AJ132" t="s" s="2">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="133" hidden="true">
-      <c r="A133" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="B133" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="C133" s="2"/>
-      <c r="D133" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E133" s="2"/>
-      <c r="F133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G133" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H133" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I133" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J133" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K133" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="L133" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O133" s="2"/>
-      <c r="P133" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q133" s="2"/>
-      <c r="R133" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S133" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T133" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U133" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V133" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W133" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X133" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y133" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="Z133" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="AA133" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB133" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC133" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD133" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE133" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF133" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="AG133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH133" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI133" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AJ133" t="s" s="2">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="134" hidden="true">
-      <c r="A134" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="C134" s="2"/>
-      <c r="D134" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E134" s="2"/>
-      <c r="F134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G134" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H134" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I134" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J134" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K134" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="L134" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="P134" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q134" s="2"/>
-      <c r="R134" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S134" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T134" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U134" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V134" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W134" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X134" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y134" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z134" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA134" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB134" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC134" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD134" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE134" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF134" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="AG134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH134" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI134" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AJ134" t="s" s="2">
-        <v>567</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ134">
+  <autoFilter ref="A1:AJ117">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15921,7 +14065,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI133">
+  <conditionalFormatting sqref="A2:AI116">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/migration/2027.0.0-alpha.6-template-v0.13.2/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
+++ b/branches/migration/2027.0.0-alpha.6-template-v0.13.2/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T21:03:23+00:00</t>
+    <t>2026-09-02T21:10:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-alpha.6-template-v0.13.2/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
+++ b/branches/migration/2027.0.0-alpha.6-template-v0.13.2/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T21:10:40+00:00</t>
+    <t>2026-09-02T21:48:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-alpha.6-template-v0.13.2/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
+++ b/branches/migration/2027.0.0-alpha.6-template-v0.13.2/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T21:48:21+00:00</t>
+    <t>2026-09-03T04:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-alpha.6-template-v0.13.2/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
+++ b/branches/migration/2027.0.0-alpha.6-template-v0.13.2/StructureDefinition-mii-pr-mikrobio-diagnostic-report.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T04:37:30+00:00</t>
+    <t>2026-09-03T05:02:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
